--- a/data/Dana anual 1935 2025 Ferreres Propatto Argentina gob datos.xlsx
+++ b/data/Dana anual 1935 2025 Ferreres Propatto Argentina gob datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5504A7D2-FC9B-C443-88ED-CF19FA6EC2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CF448F-8C2A-9041-AF02-954596173C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4560" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{7B375BBC-6C37-914E-9894-234B84AF70CF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{7B375BBC-6C37-914E-9894-234B84AF70CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>año</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Ptrigo_USA</t>
+  </si>
+  <si>
+    <t>impp_usa</t>
   </si>
 </sst>
 </file>
@@ -113,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -126,7 +129,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,10 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EFAC2A-B7AF-C84C-9A8D-AFF06A22A578}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="17">
+    <row r="1" spans="1:8" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,8 +488,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>1935</v>
       </c>
@@ -509,8 +514,11 @@
       <c r="G2" s="4">
         <v>0.85958333333333325</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>4.4057394210779064</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>1936</v>
       </c>
@@ -532,8 +540,11 @@
       <c r="G3" s="4">
         <v>0.95783333333333343</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>4.7204350940120428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>1937</v>
       </c>
@@ -555,8 +566,11 @@
       <c r="G4" s="4">
         <v>1.0713333333333332</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>5.2762612176359704</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>1938</v>
       </c>
@@ -578,8 +592,11 @@
       <c r="G5" s="4">
         <v>0.66116666666666657</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>4.7653916187169196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>1939</v>
       </c>
@@ -601,15 +618,18 @@
       <c r="G6" s="4">
         <v>0.63558333333333328</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>4.8266959705872052</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>1940</v>
       </c>
       <c r="B7" s="3">
         <v>76724</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>4.368283333333334E-13</v>
       </c>
       <c r="D7">
@@ -624,8 +644,11 @@
       <c r="G7" s="4">
         <v>0.73908333333333343</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7">
+        <v>5.165913384269456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>1941</v>
       </c>
@@ -647,8 +670,11 @@
       <c r="G8" s="4">
         <v>0.8394999999999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>5.5092177547430596</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>1942</v>
       </c>
@@ -670,8 +696,11 @@
       <c r="G9" s="4">
         <v>1.0185</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>6.4410439031714102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>1943</v>
       </c>
@@ -681,7 +710,7 @@
       <c r="C10">
         <v>4.0605500000000008E-13</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10">
         <v>9.29388136580428E-14</v>
       </c>
       <c r="E10" s="4">
@@ -693,8 +722,11 @@
       <c r="G10" s="4">
         <v>1.2733333333333334</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>6.9723482860472243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>1944</v>
       </c>
@@ -716,8 +748,11 @@
       <c r="G11" s="4">
         <v>1.4283333333333335</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11">
+        <v>7.434174403470049</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>1945</v>
       </c>
@@ -739,8 +774,11 @@
       <c r="G12" s="4">
         <v>1.4858333333333331</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12">
+        <v>7.6630439837857836</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>1946</v>
       </c>
@@ -762,8 +800,11 @@
       <c r="G13" s="4">
         <v>1.7358333333333331</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13">
+        <v>8.5008701260130284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>1947</v>
       </c>
@@ -785,8 +826,11 @@
       <c r="G14" s="4">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>10.393131120409201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>1948</v>
       </c>
@@ -808,8 +852,11 @@
       <c r="G15" s="4">
         <v>2.1491666666666664</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15">
+        <v>11.537479021987874</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>1949</v>
       </c>
@@ -831,8 +878,11 @@
       <c r="G16" s="4">
         <v>1.9166666666666667</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>10.977565941572596</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>1950</v>
       </c>
@@ -854,8 +904,11 @@
       <c r="G17" s="4">
         <v>1.9808333333333334</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>11.880783392461481</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>1951</v>
       </c>
@@ -877,8 +930,11 @@
       <c r="G18" s="4">
         <v>2.1191666666666666</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>14.94600098597579</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>1952</v>
       </c>
@@ -900,8 +956,11 @@
       <c r="G19" s="4">
         <v>2.1150000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>14.149044411662073</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>1953</v>
       </c>
@@ -923,8 +982,11 @@
       <c r="G20" s="4">
         <v>1.9891666666666667</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>13.568696547290031</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>1954</v>
       </c>
@@ -946,8 +1008,11 @@
       <c r="G21" s="4">
         <v>2.0475000000000003</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>13.850696565893344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>1955</v>
       </c>
@@ -969,8 +1034,11 @@
       <c r="G22" s="4">
         <v>2.0241666666666664</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>13.813913954771177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>1956</v>
       </c>
@@ -992,8 +1060,11 @@
       <c r="G23" s="4">
         <v>1.9758333333333333</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>14.128609627705313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>1957</v>
       </c>
@@ -1015,8 +1086,11 @@
       <c r="G24" s="4">
         <v>1.9724999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>14.212204605588674</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>1958</v>
       </c>
@@ -1038,8 +1112,11 @@
       <c r="G25" s="4">
         <v>1.7933333333333332</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25">
+        <v>13.560490712012449</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>1959</v>
       </c>
@@ -1061,8 +1138,11 @@
       <c r="G26" s="4">
         <v>1.7458333333333333</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26">
+        <v>13.311061996808199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2">
         <v>1960</v>
       </c>
@@ -1084,8 +1164,11 @@
       <c r="G27" s="4">
         <v>1.7608333333333335</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27">
+        <v>13.483202941044725</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2">
         <v>1961</v>
       </c>
@@ -1107,8 +1190,11 @@
       <c r="G28" s="4">
         <v>1.8083333333333331</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28">
+        <v>13.30052275528705</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>1962</v>
       </c>
@@ -1130,8 +1216,11 @@
       <c r="G29" s="4">
         <v>1.9583333333333333</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29">
+        <v>13.015963235199624</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>1963</v>
       </c>
@@ -1153,8 +1242,11 @@
       <c r="G30" s="4">
         <v>1.9400000000000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30">
+        <v>13.096764086592451</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>1964</v>
       </c>
@@ -1176,8 +1268,11 @@
       <c r="G31" s="4">
         <v>1.6016666666666666</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31">
+        <v>13.490229101965125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="2">
         <v>1965</v>
       </c>
@@ -1199,8 +1294,11 @@
       <c r="G32" s="4">
         <v>1.3475000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32">
+        <v>13.56400379243755</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="2">
         <v>1966</v>
       </c>
@@ -1222,8 +1320,11 @@
       <c r="G33" s="4">
         <v>1.551666666666667</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33">
+        <v>13.929364163988051</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2">
         <v>1967</v>
       </c>
@@ -1245,8 +1346,11 @@
       <c r="G34" s="4">
         <v>1.4708333333333332</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34">
+        <v>14.052321981324926</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="2">
         <v>1968</v>
       </c>
@@ -1268,8 +1372,11 @@
       <c r="G35" s="4">
         <v>1.3008333333333333</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35">
+        <v>14.213923684145724</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="2">
         <v>1969</v>
       </c>
@@ -1291,8 +1398,11 @@
       <c r="G36" s="4">
         <v>1.2549999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36">
+        <v>14.629940020623625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="2">
         <v>1970</v>
       </c>
@@ -1314,8 +1424,11 @@
       <c r="G37" s="4">
         <v>1.3308333333333333</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37">
+        <v>15.630009007273875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="2">
         <v>1971</v>
       </c>
@@ -1337,8 +1450,11 @@
       <c r="G38" s="4">
         <v>1.3599999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38">
+        <v>16.438240861454727</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="2">
         <v>1972</v>
       </c>
@@ -1360,8 +1476,11 @@
       <c r="G39" s="4">
         <v>1.5733333333333335</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39">
+        <v>17.633291851947924</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="2">
         <v>1973</v>
       </c>
@@ -1383,8 +1502,11 @@
       <c r="G40" s="4">
         <v>3.1566666666666663</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40">
+        <v>20.954275657195375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="2">
         <v>1974</v>
       </c>
@@ -1406,8 +1528,11 @@
       <c r="G41" s="4">
         <v>4.4841666666666669</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41">
+        <v>31.033587300993851</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="2">
         <v>1975</v>
       </c>
@@ -1429,8 +1554,11 @@
       <c r="G42" s="4">
         <v>3.6775000000000002</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42">
+        <v>33.826232773745524</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="2">
         <v>1976</v>
       </c>
@@ -1452,8 +1580,11 @@
       <c r="G43" s="4">
         <v>3.1458333333333335</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43">
+        <v>34.860895341889076</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="2">
         <v>1977</v>
       </c>
@@ -1475,8 +1606,11 @@
       <c r="G44" s="4">
         <v>2.29</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44">
+        <v>37.634671588317353</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="2">
         <v>1978</v>
       </c>
@@ -1498,8 +1632,11 @@
       <c r="G45" s="4">
         <v>2.8241666666666663</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45">
+        <v>40.917916941169523</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="2">
         <v>1979</v>
       </c>
@@ -1521,8 +1658,11 @@
       <c r="G46" s="4">
         <v>3.5091666666666668</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46">
+        <v>47.993876753423578</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -1544,8 +1684,11 @@
       <c r="G47" s="4">
         <v>3.8825000000000003</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47">
+        <v>61.133147907170674</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="2">
         <v>1981</v>
       </c>
@@ -1567,8 +1710,11 @@
       <c r="G48" s="4">
         <v>3.875</v>
       </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48">
+        <v>64.403813775912027</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="2">
         <v>1982</v>
       </c>
@@ -1590,8 +1736,11 @@
       <c r="G49" s="4">
         <v>3.5216666666666665</v>
       </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49">
+        <v>63.108126912532697</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="2">
         <v>1983</v>
       </c>
@@ -1613,8 +1762,11 @@
       <c r="G50" s="4">
         <v>3.5833333333333335</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50">
+        <v>60.77148773908003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="2">
         <v>1984</v>
       </c>
@@ -1636,8 +1788,11 @@
       <c r="G51" s="4">
         <v>3.4624999999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51">
+        <v>61.815584920180775</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="2">
         <v>1985</v>
       </c>
@@ -1659,8 +1814,11 @@
       <c r="G52" s="4">
         <v>3.1966666666666668</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="H52">
+        <v>60.296612213834919</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="2">
         <v>1986</v>
       </c>
@@ -1682,8 +1840,11 @@
       <c r="G53" s="4">
         <v>2.7074999999999996</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53">
+        <v>58.324778079595077</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="2">
         <v>1987</v>
       </c>
@@ -1705,8 +1866,11 @@
       <c r="G54" s="4">
         <v>2.5525000000000002</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="H54">
+        <v>62.318764284832326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="2">
         <v>1988</v>
       </c>
@@ -1728,8 +1892,11 @@
       <c r="G55" s="4">
         <v>3.3266666666666667</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55">
+        <v>65.764108869962186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="2">
         <v>1989</v>
       </c>
@@ -1751,8 +1918,11 @@
       <c r="G56" s="4">
         <v>3.8758333333333335</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="H56">
+        <v>71.82016813835736</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="2">
         <v>1990</v>
       </c>
@@ -1774,8 +1944,11 @@
       <c r="G57" s="4">
         <v>2.9808333333333334</v>
       </c>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="H57">
+        <v>74.146165068363501</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="2">
         <v>1991</v>
       </c>
@@ -1797,8 +1970,11 @@
       <c r="G58" s="4">
         <v>2.7383333333333333</v>
       </c>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="H58">
+        <v>74.196294312544651</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="2">
         <v>1992</v>
       </c>
@@ -1820,8 +1996,11 @@
       <c r="G59" s="4">
         <v>3.3824999999999998</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59">
+        <v>74.807755504436315</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="2">
         <v>1993</v>
       </c>
@@ -1843,8 +2022,11 @@
       <c r="G60" s="4">
         <v>3.2058333333333335</v>
       </c>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="H60">
+        <v>74.636871508379798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="2">
         <v>1994</v>
       </c>
@@ -1866,8 +2048,11 @@
       <c r="G61" s="4">
         <v>3.5158333333333331</v>
       </c>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61">
+        <v>75.892211633256579</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="2">
         <v>1995</v>
       </c>
@@ -1889,8 +2074,11 @@
       <c r="G62" s="4">
         <v>4.0925000000000002</v>
       </c>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62">
+        <v>79.316464015773832</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="2">
         <v>1996</v>
       </c>
@@ -1912,8 +2100,11 @@
       <c r="G63" s="4">
         <v>4.7666666666666666</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="H63">
+        <v>80.118304304962095</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="2">
         <v>1997</v>
       </c>
@@ -1935,8 +2126,11 @@
       <c r="G64" s="4">
         <v>3.7124999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64">
+        <v>78.146565888925323</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="2">
         <v>1998</v>
       </c>
@@ -1958,8 +2152,11 @@
       <c r="G65" s="4">
         <v>2.9033333333333333</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65">
+        <v>73.434111074597411</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="2">
         <v>1999</v>
       </c>
@@ -1981,8 +2178,11 @@
       <c r="G66" s="4">
         <v>2.5758333333333336</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66">
+        <v>74.065067367729142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="2">
         <v>2000</v>
       </c>
@@ -2004,8 +2204,11 @@
       <c r="G67" s="4">
         <v>2.5683333333333334</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67">
+        <v>78.869536641472166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="2">
         <v>2001</v>
       </c>
@@ -2027,8 +2230,11 @@
       <c r="G68" s="4">
         <v>2.8299999999999996</v>
       </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68">
+        <v>76.07624055208673</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="2">
         <v>2002</v>
       </c>
@@ -2050,8 +2256,11 @@
       <c r="G69" s="4">
         <v>3.4058333333333337</v>
       </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69">
+        <v>74.196516595464928</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="2">
         <v>2003</v>
       </c>
@@ -2073,8 +2282,11 @@
       <c r="G70" s="4">
         <v>3.4449999999999998</v>
       </c>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70">
+        <v>76.385146237265829</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="2">
         <v>2004</v>
       </c>
@@ -2096,8 +2308,11 @@
       <c r="G71" s="4">
         <v>3.5683333333333334</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71">
+        <v>80.69010844561285</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="2">
         <v>2005</v>
       </c>
@@ -2119,8 +2334,11 @@
       <c r="G72" s="4">
         <v>3.3591666666666673</v>
       </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72">
+        <v>86.749917844232627</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="2">
         <v>2006</v>
       </c>
@@ -2142,8 +2360,11 @@
       <c r="G73" s="4">
         <v>4.0333333333333332</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73">
+        <v>90.976010515938171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="2">
         <v>2007</v>
       </c>
@@ -2165,8 +2386,11 @@
       <c r="G74" s="4">
         <v>5.7591666666666663</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74">
+        <v>94.814327965823168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="2">
         <v>2008</v>
       </c>
@@ -2188,8 +2412,11 @@
       <c r="G75" s="4">
         <v>8.019166666666667</v>
       </c>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75">
+        <v>105.72461386789327</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="2">
         <v>2009</v>
       </c>
@@ -2211,8 +2438,11 @@
       <c r="G76" s="4">
         <v>5.3041666666666663</v>
       </c>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76">
+        <v>93.572132763719978</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="2">
         <v>2010</v>
       </c>
@@ -2234,8 +2464,11 @@
       <c r="G77" s="4">
         <v>5.1150000000000002</v>
       </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77">
+        <v>100.00000000000009</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="2">
         <v>2011</v>
       </c>
@@ -2257,8 +2490,11 @@
       <c r="G78" s="4">
         <v>7.4366666666666674</v>
       </c>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78">
+        <v>110.90371344068376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="2">
         <v>2012</v>
       </c>
@@ -2280,8 +2516,11 @@
       <c r="G79" s="4">
         <v>7.5983333333333327</v>
       </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79">
+        <v>111.21261912586274</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="2">
         <v>2013</v>
       </c>
@@ -2303,8 +2542,11 @@
       <c r="G80" s="4">
         <v>7.315833333333333</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80">
+        <v>109.99014130791974</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="2">
         <v>2014</v>
       </c>
@@ -2326,8 +2568,11 @@
       <c r="G81" s="4">
         <v>6.3333333333333339</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81">
+        <v>108.807098258298</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="2">
         <v>2015</v>
       </c>
@@ -2349,8 +2594,11 @@
       <c r="G82" s="4">
         <v>5.2758333333333338</v>
       </c>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82">
+        <v>97.739073282944503</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="2">
         <v>2016</v>
       </c>
@@ -2372,8 +2620,11 @@
       <c r="G83" s="4">
         <v>4.1091666666666669</v>
       </c>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="H83">
+        <v>94.485704896483796</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="2">
         <v>2017</v>
       </c>
@@ -2395,8 +2646,11 @@
       <c r="G84" s="4">
         <v>4.4366666666666674</v>
       </c>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84">
+        <v>97.226421294774923</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="2">
         <v>2018</v>
       </c>
@@ -2418,8 +2672,11 @@
       <c r="G85" s="4">
         <v>5.1433333333333326</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85">
+        <v>100.26947091685859</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="2">
         <v>2019</v>
       </c>
@@ -2441,8 +2698,11 @@
       <c r="G86" s="4">
         <v>4.7433333333333332</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86">
+        <v>98.994413407821256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="2">
         <v>2020</v>
       </c>
@@ -2464,8 +2724,11 @@
       <c r="G87" s="4">
         <v>4.8574999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="H87">
+        <v>96.523167926388467</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="2">
         <v>2021</v>
       </c>
@@ -2487,8 +2750,11 @@
       <c r="G88" s="4">
         <v>6.84</v>
       </c>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="H88">
+        <v>105.060795267828</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="2">
         <v>2022</v>
       </c>
@@ -2510,8 +2776,11 @@
       <c r="G89" s="4">
         <v>9.3000000000000007</v>
       </c>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H89">
+        <v>113.95333552415376</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="2">
         <v>2023</v>
       </c>
@@ -2533,8 +2802,11 @@
       <c r="G90" s="4">
         <v>7.6691666666666674</v>
       </c>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="H90">
+        <v>110.43049622083474</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="2">
         <v>2024</v>
       </c>
@@ -2557,7 +2829,7 @@
         <v>5.7991666666666672</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:8">
       <c r="A92" s="2">
         <v>2025</v>
       </c>
